--- a/salon_forms/025_covid_19_salon_services_consent_form--salon_forms.xlsx
+++ b/salon_forms/025_covid_19_salon_services_consent_form--salon_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>covid_19_salon_services_consent_form</t>
+          <t>Covid 19 Salon Services Consent Form</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>contact_name</t>
+          <t>Contact Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>email_address</t>
+          <t>Email Address</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>service_type</t>
+          <t>have_you_traveled_recently</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>service_type</t>
+          <t>Have you traveled recently?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>have_you_traveled_recently</t>
+          <t>have_you_visited_a_high_risk_location</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>have_you_traveled_recently</t>
+          <t>Have you visited a high-risk location?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>symptoms</t>
+          <t>recent_travel_history</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>symptoms</t>
+          <t>Recent Travel History</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>have_you_visited_a_high_risk_location</t>
+          <t>have_you_been_in_close_contact</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>have_you_visited_a_high_risk_location</t>
+          <t>Have you been in close contact?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>recent_travel_history</t>
+          <t>have_you_been_tested</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>recent_travel_history</t>
+          <t>Have you been tested?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>contact_tracing_status</t>
+          <t>last_test_result</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contact_tracing_status</t>
+          <t>Last Test Result</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>have_you_been_in_close_contact</t>
+          <t>have_you_been_in_contact_with_someone_sick</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>have_you_been_in_close_contact</t>
+          <t>Have you been in contact with someone sick?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>have_you_been_tested</t>
+          <t>have_you_been_in_contact_with_someone_with_covid</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>have_you_been_tested</t>
+          <t>Have you been in contact with someone with COVID-19?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>last_test_result</t>
+          <t>have_you_been_in_close_contact_with_someone_with_symptoms</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>last_test_result</t>
+          <t>Have you been in close contact with someone with COVID-19 symptoms?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>have_you_visited_a_high_risk_location</t>
+          <t>have_you_been_in_contact_with_someone_with_covid_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>have_you_visited_a_high_risk_location</t>
+          <t>Have You Been In Contact With Someone With Covid 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>have_you_traveled_to</t>
+          <t>have_you_been_in_close_contact_with_someone_diagnosed_with_covid</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>have_you_traveled_to</t>
+          <t>Have you been in close contact with someone diagnosed with COVID-19?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>have_you_been_in_contact_with_anyone_sick</t>
+          <t>have_you_been_in_contact_with_someone_diagnosed_with_covid</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>have_you_been_in_contact_with_anyone_sick</t>
+          <t>Have you been in contact with someone diagnosed with COVID-19?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,205 +883,44 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>have_you_been_in_contact_with_someone_who_has_covid</t>
+          <t>service_type</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>have_you_been_in_contact_with_someone_who_has_covid</t>
+          <t>Service Type</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>have_you_been_in_contact_with_someone_with_covid</t>
+          <t>recent_travel_history_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>have_you_been_in_contact_with_someone_with_covid</t>
+          <t>Recent Travel History 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_diagnosed_with_covid</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_diagnosed_with_covid</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_sick_contacts</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_sick_contacts</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_with_covid_symptoms</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_with_covid_symptoms</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_with_symptoms</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_with_symptoms</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>have_you_been_in_close_contact_with_someone_with_symptoms</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>have_you_been_in_close_contact_with_someone_with_symptoms</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_diagnosed_with_covid</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_diagnosed_with_covid</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_with_covid_symptoms</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_with_covid_symptoms</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,646 +965,442 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>have_you_traveled_recently_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>have_you_traveled_recently_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>have_you_traveled_recently_choices</t>
+          <t>have_you_visited_a_high_risk_location_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>have_you_traveled_recently_choices</t>
+          <t>have_you_visited_a_high_risk_location_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>have_you_visited_a_high_risk_location_choices</t>
+          <t>have_you_been_in_close_contact_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>have_you_visited_a_high_risk_location_choices</t>
+          <t>have_you_been_in_close_contact_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>contact_tracing_status_choices</t>
+          <t>have_you_been_tested_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>contact_tracing_status_choices</t>
+          <t>have_you_been_tested_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>have_you_been_in_close_contact_choices</t>
+          <t>last_test_result_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>have_you_been_in_close_contact_choices</t>
+          <t>last_test_result_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>have_you_been_tested_choices</t>
+          <t>have_you_been_in_contact_with_someone_sick_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>have_you_been_tested_choices</t>
+          <t>have_you_been_in_contact_with_someone_sick_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>last_test_result_choices</t>
+          <t>have_you_been_in_contact_with_someone_with_covid_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>last_test_result_choices</t>
+          <t>have_you_been_in_contact_with_someone_with_covid_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>have_you_visited_a_high_risk_location_choices</t>
+          <t>have_you_been_in_close_contact_with_someone_with_symptoms_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>have_you_visited_a_high_risk_location_choices</t>
+          <t>have_you_been_in_close_contact_with_someone_with_symptoms_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>have_you_traveled_to_choices</t>
+          <t>have_you_been_in_contact_with_someone_with_covid_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>have_you_traveled_to_choices</t>
+          <t>have_you_been_in_contact_with_someone_with_covid_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>have_you_been_in_contact_with_anyone_sick_choices</t>
+          <t>have_you_been_in_close_contact_with_someone_diagnosed_with_covid_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>have_you_been_in_contact_with_anyone_sick_choices</t>
+          <t>have_you_been_in_close_contact_with_someone_diagnosed_with_covid_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>have_you_been_in_contact_with_someone_who_has_covid_choices</t>
+          <t>have_you_been_in_contact_with_someone_diagnosed_with_covid_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>have_you_been_in_contact_with_someone_who_has_covid_choices</t>
+          <t>have_you_been_in_contact_with_someone_diagnosed_with_covid_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>have_you_been_in_contact_with_someone_with_covid_choices</t>
+          <t>service_type_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>haircut</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Haircut</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>have_you_been_in_contact_with_someone_with_covid_choices</t>
+          <t>service_type_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Color</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>have_you_been_in_contact_with_someone_diagnosed_with_covid_choices</t>
+          <t>service_type_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>chemical_service</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Chemical Service</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>have_you_been_in_contact_with_someone_diagnosed_with_covid_choices</t>
+          <t>service_type_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>waxing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_sick_contacts_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_sick_contacts_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_with_covid_symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_with_covid_symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_with_symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_with_symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>have_you_been_in_close_contact_with_someone_with_symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>have_you_been_in_close_contact_with_someone_with_symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_diagnosed_with_covid_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_diagnosed_with_covid_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_with_covid_symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>have_you_been_in_contact_with_someone_with_covid_symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>option2</t>
+          <t>Waxing</t>
         </is>
       </c>
     </row>
